--- a/results/job_matches_2026-09-30.xlsx
+++ b/results/job_matches_2026-09-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Systems Engineer, SME</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cricut</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>24.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, IAM, RDS, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0116d4b4ca656c94</t>
+          <t>https://www.indeed.com/viewjob?jk=402992014bd3bfa3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Apartments.com - Irvine, CA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Event Hubs, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53ace7c739bbef4</t>
+          <t>https://www.indeed.com/viewjob?jk=9b290da3929fa0b4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer II - Apartments.com - Irvine, CA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Cricut</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0ca5cc30971dc02</t>
+          <t>https://www.indeed.com/viewjob?jk=0116d4b4ca656c94</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Developer &amp; Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WISEcode</t>
+          <t>Signant Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Medallion Architecture, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961c34d9312bd45f</t>
+          <t>https://www.indeed.com/viewjob?jk=7f8cf55805f4851f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Apartments.com - Irvine, CA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>University of Colorado</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aurora, CO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Scala, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551c49c9aa5e5584</t>
+          <t>https://www.indeed.com/viewjob?jk=a53ace7c739bbef4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer 5</t>
+          <t>Data Engineer II - Apartments.com - Irvine, CA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,129 +671,129 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=660e2cf474b4e061</t>
+          <t>https://www.indeed.com/viewjob?jk=a0ca5cc30971dc02</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Delta Live Tables, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98b9323fde0e076c</t>
+          <t>https://www.indeed.com/viewjob?jk=97fa3ea752ece8fd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer 5</t>
+          <t>Software Developer &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>WISEcode</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b54c7cf7e0d49278</t>
+          <t>https://www.indeed.com/viewjob?jk=961c34d9312bd45f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>University of Colorado</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Aurora, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, ECS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73b249b48cff4978</t>
+          <t>https://www.indeed.com/viewjob?jk=551c49c9aa5e5584</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pittsburg, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8788c118957a8b6</t>
+          <t>https://www.indeed.com/viewjob?jk=660e2cf474b4e061</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pittsburg, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab0ee907185e5f01</t>
+          <t>https://www.indeed.com/viewjob?jk=98b9323fde0e076c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Distributed data &amp; AWS) (Cloud Operations Resilience Engineering)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Pittsburg, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f43423f60faa323d</t>
+          <t>https://www.indeed.com/viewjob?jk=d8788c118957a8b6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Zifo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburg, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, RDS, Databricks, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d707249d6f4c2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=ab0ee907185e5f01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JACK'S</t>
+          <t>Zifo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, IAM, RDS, Google Cloud Platform, Cloud Storage, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5920428f1dd8e6b7</t>
+          <t>https://www.indeed.com/viewjob?jk=1d707249d6f4c2b1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud and DevOps</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>JACK'S</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, Azure, GCP, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, IAM, RDS, Google Cloud Platform, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b52c9ef8ab310ca</t>
+          <t>https://www.indeed.com/viewjob?jk=5920428f1dd8e6b7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Software Engineer - Cloud and DevOps</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Zions Bancorporation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Spark, PySpark, Scala, SQL Server, MongoDB</t>
+          <t>AWS, API Gateway, IAM, Azure, GCP, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a31aef3876037c</t>
+          <t>https://www.indeed.com/viewjob?jk=9b52c9ef8ab310ca</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS &amp; Azure) - Contract-to-Hire</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cruz Street</t>
+          <t>arrivia</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vero Beach, FL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, Data Factory</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=339fc28aca922522</t>
+          <t>https://www.indeed.com/viewjob?jk=53d44b35a8a09b64</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>American Lung Association</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7ef180f361a4b8</t>
+          <t>https://www.indeed.com/viewjob?jk=70ab61efb1bae2af</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (AWS &amp; Azure) - Contract-to-Hire</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Southern Hobby Distribution</t>
+          <t>Cruz Street</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vero Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb16d38559fc0b69</t>
+          <t>https://www.indeed.com/viewjob?jk=339fc28aca922522</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer - Pre-trade (Gas &amp; Power Industry)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Talan</t>
+          <t>American Lung Association</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, Azure, Data Factory, GCP, BigQuery</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe858dfd726768d</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7ef180f361a4b8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Backend Software Engineer II – AWS &amp; Data Platforms</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Southern Hobby Distribution</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1c49163f9df6e3</t>
+          <t>https://www.indeed.com/viewjob?jk=cb16d38559fc0b69</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C,C++, Python, Golang Developer</t>
+          <t>Senior Cloud Software Engineer - Pre-trade (Gas &amp; Power Industry)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Talan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, Azure, Data Factory, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adc654a7b5482d94</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe858dfd726768d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I</t>
+          <t>Backend Software Engineer II – AWS &amp; Data Platforms</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6882c6ed46ad5482</t>
+          <t>https://www.indeed.com/viewjob?jk=2b1c49163f9df6e3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Software Engineer I</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sony</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>EMR, Kinesis, Athena, RDS, Hadoop, Scala, Kafka, Snowflake, Oracle, DynamoDB</t>
+          <t>AWS, RDS, HBase, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c96ed04a9d166985</t>
+          <t>https://www.indeed.com/viewjob?jk=6882c6ed46ad5482</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bollinger Shipyards</t>
+          <t>Precision Analytical Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Raceland, LA, US USA</t>
+          <t>McMinnville, OR, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Oracle, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664254325a625205</t>
+          <t>https://www.indeed.com/viewjob?jk=dd324299a23feb72</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III: Backend C#</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Bollinger Shipyards</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raceland, LA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,69 +1431,69 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b9180a14620aa14</t>
+          <t>https://www.indeed.com/viewjob?jk=664254325a625205</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III: Backend C#</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38f351aee1da6602</t>
+          <t>https://www.indeed.com/viewjob?jk=8b9180a14620aa14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dbffb9333bd2fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=38f351aee1da6602</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Databricks Engineer - Contractor (contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0f788a895458b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=5dbffb9333bd2fe0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Technical Architect Wealth And Retirement</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Bridgenext</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Event Hubs, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed859e450f4fb1f8</t>
+          <t>https://www.indeed.com/viewjob?jk=4cbdbb96af073d71</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Database Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Verra Mobility</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, dbt</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, Kafka, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4a511c8a3a07c3</t>
+          <t>https://www.indeed.com/viewjob?jk=ed859e450f4fb1f8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Technical Architect Wealth And Retirement</t>
+          <t>Sr. Database Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bridgenext</t>
+          <t>Verra Mobility</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Event Hubs, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cbdbb96af073d71</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4a511c8a3a07c3</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Medpace</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d105c911a496d46</t>
+          <t>https://www.indeed.com/viewjob?jk=1d80e20e6c49d29b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Analyst Engineer - Snowflake Expert</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>TKC Holdings</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9315f3e60bfa6075</t>
+          <t>https://www.indeed.com/viewjob?jk=0839459de9ce2dea</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Developer – .NET Full Stack</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a0b6bcda04fafa</t>
+          <t>https://www.indeed.com/viewjob?jk=9f7de99645ec71a2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI-Native Development Platform Engineer Intern, MS - Summer 2027</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8645c5596f3bb194</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb60ceb5f3d080b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, Power BI, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f348d8dd12d13dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=fe97c58bd1f9ed9b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, Power BI, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85f353e2816c2a63</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5f97b462b22e62</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Ontario, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Scala, Kafka, PostgreSQL, MongoDB, Data Modeling, ETL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,242 +2176,242 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6337d0b5fa6d92</t>
+          <t>https://www.indeed.com/viewjob?jk=35a4f37408022609</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Junior Business Intelligence Engineer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Medpace</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d80e20e6c49d29b</t>
+          <t>https://www.indeed.com/viewjob?jk=9a830e46d79d3579</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Enterprise Analytics</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Inland Real Estate Group of Companies, Inc.</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1fbedd6c9d0d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=1f9b93235e29f6c1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Enterprise Analytics</t>
+          <t>API Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Inland Real Estate Group of Companies, Inc.</t>
+          <t>SafelyYou</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, API Gateway, ECS, RDS, Spark, Scala, Spark Streaming, Kafka, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=519dcdfdfb4bef2a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b87640e62e54b64</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, Enterprise Analytics</t>
+          <t>Senior Software Architect – Client &amp; Technical Solutions</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The Inland Real Estate Group of Companies, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1d075b9f067a1b</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2398bae43cfca4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Analyst Engineer - Snowflake Expert</t>
+          <t>Specialist Solutions Architect - AWS Infrastructure &amp; Platform</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TKC Holdings</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0839459de9ce2dea</t>
+          <t>https://www.indeed.com/viewjob?jk=76c080f60278d6dc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI-Native Development Platform Engineer Intern, MS - Summer 2027</t>
+          <t>Data Engineer I - Data Platform</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb60ceb5f3d080b</t>
+          <t>https://www.indeed.com/viewjob?jk=b7daae54db1e425f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Databricks Data Engineer (Chicago Area)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Bilink Corp</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, Power BI, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe97c58bd1f9ed9b</t>
+          <t>https://www.indeed.com/viewjob?jk=2cc3f410679dfa32</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Solution Architect – Solutions and Platform Advisory</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Trianz</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, Power BI, Splunk, CI/CD</t>
+          <t>IAM, RDS, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5f97b462b22e62</t>
+          <t>https://www.indeed.com/viewjob?jk=825c83cc17a2a9e3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Java Engineer – Agentic AI Driven Development</t>
+          <t>Data Architect - Healthcare Insights, Revenue Cycle</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Maven, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,19 +2491,19 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fadbf39a366c1e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=b58dd53022f160e8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect - Healthcare Insights, Pharmacy</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2512,11 +2512,11 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Azure, Data Factory, Databricks, Hadoop, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e16b8afdb689b5</t>
+          <t>https://www.indeed.com/viewjob?jk=cae3580058d6b9fa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Security AI DevSecOps Engineer</t>
+          <t>Senior Dev Ops Engineer (SYS ADM 4 TX)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Regional Finance</t>
+          <t>UC Davis</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, MySQL, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abda70656eba396b</t>
+          <t>https://www.indeed.com/viewjob?jk=a35d797a405aa8a0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Go, AWS)</t>
+          <t>Concentra DevOps Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,102 +2596,102 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbf885ed4904a21</t>
+          <t>https://www.indeed.com/viewjob?jk=b87121ab466a00f3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Go, AWS)</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e44d3b7e0c07709d</t>
+          <t>https://www.indeed.com/viewjob?jk=7f774f78f05e811f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Relativity</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Spark, Scala, Kafka, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Power BI, MLOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=423eda1e0efbb045</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fcc3fc97e62735</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Spark, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a830e46d79d3579</t>
+          <t>https://www.indeed.com/viewjob?jk=dbbbfb150a6dcd5b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f9b93235e29f6c1</t>
+          <t>https://www.indeed.com/viewjob?jk=34ed24d87685f8d1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Architect – Client &amp; Technical Solutions</t>
+          <t>Full-Stack Engineer 4 (Nodejs, Angularjs, Java)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2398bae43cfca4</t>
+          <t>https://www.indeed.com/viewjob?jk=9b68e3f744cf85a2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>API Architect</t>
+          <t>AI Engineer Senior | Hybrid</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SafelyYou</t>
+          <t>Allianz</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, ECS, RDS, Spark, Scala, Spark Streaming, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ELT, MLflow, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b87640e62e54b64</t>
+          <t>https://www.indeed.com/viewjob?jk=8e49db045a45c992</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Cloud Software Engineer (On-site)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>All IT Solutions LLC</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcb630341625dadf</t>
+          <t>https://www.indeed.com/viewjob?jk=faa4e2a92b1f4e69</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Architect – Global Information Security</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a798b66406a564</t>
+          <t>https://www.indeed.com/viewjob?jk=99e4f1fca016648f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - AWS Infrastructure &amp; Platform</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c080f60278d6dc</t>
+          <t>https://www.indeed.com/viewjob?jk=de4927f7351b05ce</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer I - Data Platform</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7daae54db1e425f</t>
+          <t>https://www.indeed.com/viewjob?jk=58079e817de4277e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer (Chicago Area)</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bilink Corp</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cc3f410679dfa32</t>
+          <t>https://www.indeed.com/viewjob?jk=83176228c53939c3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Solution Architect – Solutions and Platform Advisory</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Trianz</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>IAM, RDS, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=825c83cc17a2a9e3</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c93b5fec88654f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Engineer - Billing Platform *HYBRID*</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Step Functions, IAM, RDS, Spark, SQL Server, dbt, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e97b6f30fb82e5b9</t>
+          <t>https://www.indeed.com/viewjob?jk=151ea1e60e7bac7b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Engineer - Billing Platform *HYBRID*</t>
+          <t>Engineer II/III (Claims)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>MAPFRE Insurance</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Webster, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Scala, Oracle, SQL Server, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,67 +3086,67 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba596d7725923fc</t>
+          <t>https://www.indeed.com/viewjob?jk=d3b375ce161bec97</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Engineer - Billing Platform *HYBRID*</t>
+          <t>Senior Java Developer--NAOP (New Account Opening Platform)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Zions Bancorporation</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eab745942572e67</t>
+          <t>https://www.indeed.com/viewjob?jk=93eb43aa251ecf3f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Enterprise Data Solution Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>Harman</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Novi, MI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8730847460692f</t>
+          <t>https://www.indeed.com/viewjob?jk=1f79d13cbfcddf00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Oracle On prem to AWS Migration Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Splunk, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f24c00939e5ed75c</t>
+          <t>https://www.indeed.com/viewjob?jk=5e01673a28815832</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>Harrington Process Solutions</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Chino, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f774f78f05e811f</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8614d77d4401e0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Architect - Healthcare Insights, Revenue Cycle</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Harrington Process Solutions</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chino, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b58dd53022f160e8</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0cad18cf1700f2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Architect - Healthcare Insights, Pharmacy</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Cricut</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,102 +3296,102 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae3580058d6b9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=6b81ccfe00621caf</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer (SYS ADM 4 TX)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>UC Davis</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, MySQL, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>API Gateway, RDS, Scala, Splunk, MLflow, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35d797a405aa8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6fb706820b4a71cf</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Concentra DevOps Engineer II</t>
+          <t>Senior Big Data Engineers</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Carrollton, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87121ab466a00f3</t>
+          <t>https://www.indeed.com/viewjob?jk=cde128110938c0cc</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer Senior (Python/SQL)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Power BI, MLOps</t>
+          <t>RDS, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fcc3fc97e62735</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe5f4121021f1f1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Graph Engineer (Neo4j, Python, Cloud)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ed24d87685f8d1</t>
+          <t>https://www.indeed.com/viewjob?jk=4abb4feae415dce7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Nodejs, Angularjs, Java)</t>
+          <t>Graph Engineer (Neo4j, Python, Cloud)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b68e3f744cf85a2</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa843bcedcc0999</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AI Engineer Senior | Hybrid</t>
+          <t>Sr AI Platform Engineer- Hybrid in Alpharetta, GA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Allianz</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ELT, MLflow, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,19 +3506,19 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e49db045a45c992</t>
+          <t>https://www.indeed.com/viewjob?jk=1950a9dc92f87ca2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer - Football</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Tennessee Titans</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3527,11 +3527,11 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e4f1fca016648f</t>
+          <t>https://www.indeed.com/viewjob?jk=7558bccd6171065e</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Data Engineer (Generative AI &amp; Healthcare Data)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Altarum</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, MLflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83176228c53939c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1f49e9b26d98bb56</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Software Engineer- Data Platform</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>UPLIGHT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Databricks, Unity Catalog, GCP, Spark, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c93b5fec88654f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ebb44c59e3216f7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, IAM, RDS, Spark, SQL Server, dbt, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,67 +3646,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151ea1e60e7bac7b</t>
+          <t>https://www.indeed.com/viewjob?jk=990c95bc91fe1ded</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Engineer II/III (Claims)</t>
+          <t>Senior Site Reliability Engineer (US)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>Climavision</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Oracle, SQL Server, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b375ce161bec97</t>
+          <t>https://www.indeed.com/viewjob?jk=d84804cb26e94786</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Developer Tools &amp; SDKs</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,67 +3716,67 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e01673a28815832</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed762a7f7392ce8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Java Developer--NAOP (New Account Opening Platform)</t>
+          <t>Sr AI/ML Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93eb43aa251ecf3f</t>
+          <t>https://www.indeed.com/viewjob?jk=da5656fa0a41712d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Enterprise Data Solution Architect</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Harman</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Novi, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f79d13cbfcddf00</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab467c318fd6c96</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Engineer, Technology I</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, MongoDB, DynamoDB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8e935360a6c84ae</t>
+          <t>https://www.indeed.com/viewjob?jk=b819455b2c6a14c4</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior .NET Application Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Harrington Process Solutions</t>
+          <t>ASSYST, Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chino, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8614d77d4401e0</t>
+          <t>https://www.indeed.com/viewjob?jk=6237006eb649fb5e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Harrington Process Solutions</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chino, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Jenkins, Git, SQL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,67 +3891,67 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0cad18cf1700f2</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9a01bf4bcd322b</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Engineer .NET</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a7223f2600dffbd</t>
+          <t>https://www.indeed.com/viewjob?jk=c56bf3e137b2717d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Engineer .NET</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cricut</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b81ccfe00621caf</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd288a3d91533b1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Cyber)</t>
+          <t>Senior Engineer .NET</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50df5c630173a79e</t>
+          <t>https://www.indeed.com/viewjob?jk=d40253975ae472fc</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Cyber)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff744ea970f680d</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8da3c50569b80d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Specialist Solutions Architect - Azure Infrastructure &amp; Platform</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,637 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544c5bd52b84d1f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Big Data Engineers</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Carrollton, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka, NoSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cde128110938c0cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Data Engineer Senior (Python/SQL)</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>PNC Financial Services Group</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Lakewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe5f4121021f1f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Data Engineer (Generative AI &amp; Healthcare Data)</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Altarum</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, MLflow</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1f49e9b26d98bb56</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Software Engineer- Data Platform</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>UPLIGHT</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Unity Catalog, GCP, Spark, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9ebb44c59e3216f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>OpenShift Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=990c95bc91fe1ded</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>KBX</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Green Bay, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d82ffb5eaa627d9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>KBX</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Wichita, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, ECS, IAM, RDS, Scala, Kafka, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e7dd4a9a7ed2c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Data Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b819455b2c6a14c4</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Senior .NET Application Architect</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>ASSYST, Inc.</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6237006eb649fb5e</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Congruity360</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Fall River, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, MongoDB, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f114fc360e91007e</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Engineer .NET</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c56bf3e137b2717d</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior Engineer .NET</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd288a3d91533b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Senior Engineer .NET</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d40253975ae472fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Software Developer, Full Stack</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>RS21: A Data Science and Visualization Company</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dcef4ca76cf82651</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Doral, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, Jenkins, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2c19227b36b945</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Truist</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8da3c50569b80d</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Specialist Solutions Architect - Azure Infrastructure &amp; Platform</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=9d283def45f7dc44</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Power BI, MLOps, MLflow, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e34ff016d0be98fe</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-30.xlsx
+++ b/results/job_matches_2026-09-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=660e2cf474b4e061</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a88e47fd9a09b1</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98b9323fde0e076c</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1c8cb0925460a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pittsburg, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8788c118957a8b6</t>
+          <t>https://www.indeed.com/viewjob?jk=e514f15ff0b1be4b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pittsburg, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab0ee907185e5f01</t>
+          <t>https://www.indeed.com/viewjob?jk=68101adf03f8ea37</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zifo</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, RDS, Databricks, Spark</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d707249d6f4c2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=660e2cf474b4e061</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JACK'S</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, IAM, RDS, Google Cloud Platform, Cloud Storage, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,77 +986,77 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5920428f1dd8e6b7</t>
+          <t>https://www.indeed.com/viewjob?jk=98b9323fde0e076c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud and DevOps</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Pittsburg, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, Azure, GCP, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b52c9ef8ab310ca</t>
+          <t>https://www.indeed.com/viewjob?jk=d8788c118957a8b6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>arrivia</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Pittsburg, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d44b35a8a09b64</t>
+          <t>https://www.indeed.com/viewjob?jk=ab0ee907185e5f01</t>
         </is>
       </c>
     </row>
@@ -1068,20 +1068,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Zifo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70ab61efb1bae2af</t>
+          <t>https://www.indeed.com/viewjob?jk=1d707249d6f4c2b1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS &amp; Azure) - Contract-to-Hire</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cruz Street</t>
+          <t>JACK'S</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vero Beach, FL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, Data Factory</t>
+          <t>AWS, Lambda, Redshift, Athena, S3, IAM, RDS, Google Cloud Platform, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=339fc28aca922522</t>
+          <t>https://www.indeed.com/viewjob?jk=5920428f1dd8e6b7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-stack Engineer 5 (Java, Spring, Kafka, CI/CD, AI tools, Glue, RDS, DynamoDB) (Enterprise Platforms Technology )</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>American Lung Association</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Dataflow, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7ef180f361a4b8</t>
+          <t>https://www.indeed.com/viewjob?jk=d7d57da68f94cf58</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Cloud and DevOps</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Southern Hobby Distribution</t>
+          <t>Zions Bancorporation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
+          <t>AWS, API Gateway, IAM, Azure, GCP, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb16d38559fc0b69</t>
+          <t>https://www.indeed.com/viewjob?jk=9b52c9ef8ab310ca</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer - Pre-trade (Gas &amp; Power Industry)</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Talan</t>
+          <t>arrivia</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, Azure, Data Factory, GCP, BigQuery</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe858dfd726768d</t>
+          <t>https://www.indeed.com/viewjob?jk=53d44b35a8a09b64</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Backend Software Engineer II – AWS &amp; Data Platforms</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1c49163f9df6e3</t>
+          <t>https://www.indeed.com/viewjob?jk=70ab61efb1bae2af</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I</t>
+          <t>Data Engineer (AWS &amp; Azure) - Contract-to-Hire</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Cruz Street</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Vero Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6882c6ed46ad5482</t>
+          <t>https://www.indeed.com/viewjob?jk=339fc28aca922522</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Developer / Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Lung Association</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, RDS, Hadoop, Hive</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=925e167443880f65</t>
+          <t>https://www.indeed.com/viewjob?jk=7a7ef180f361a4b8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (HYBRID)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>Southern Hobby Distribution</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ea6449546ca7a9</t>
+          <t>https://www.indeed.com/viewjob?jk=cb16d38559fc0b69</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Cloud Software Engineer - Pre-trade (Gas &amp; Power Industry)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Precision Analytical Inc</t>
+          <t>Talan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>McMinnville, OR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, Scala</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, Azure, Data Factory, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd324299a23feb72</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe858dfd726768d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Software Engineer II – AWS &amp; Data Platforms</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bollinger Shipyards</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Raceland, LA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Oracle, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664254325a625205</t>
+          <t>https://www.indeed.com/viewjob?jk=2b1c49163f9df6e3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III: Backend C#</t>
+          <t>Sr Software Engineer I</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server</t>
+          <t>AWS, RDS, HBase, Scala, Kafka, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b9180a14620aa14</t>
+          <t>https://www.indeed.com/viewjob?jk=6882c6ed46ad5482</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Developer / Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, RDS, Hadoop, Hive</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38f351aee1da6602</t>
+          <t>https://www.indeed.com/viewjob?jk=925e167443880f65</t>
         </is>
       </c>
     </row>
@@ -1523,20 +1523,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Bollinger Shipyards</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Raceland, LA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,94 +1546,94 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dbffb9333bd2fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=664254325a625205</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Technical Architect Wealth And Retirement</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bridgenext</t>
+          <t>Precision Analytical Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>McMinnville, OR, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Event Hubs, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cbdbb96af073d71</t>
+          <t>https://www.indeed.com/viewjob?jk=dd324299a23feb72</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Software Engineer III: Backend C#</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed859e450f4fb1f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8b9180a14620aa14</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Database Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Verra Mobility</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, dbt</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4a511c8a3a07c3</t>
+          <t>https://www.indeed.com/viewjob?jk=38f351aee1da6602</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Databricks, HDFS, Hive, Spark, PySpark, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f7e1ef8e1fdbe0</t>
+          <t>https://www.indeed.com/viewjob?jk=5dbffb9333bd2fe0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Intern</t>
+          <t>Enterprise Data- Data Engineer I</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>GBU Life</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Databricks, HDFS, Hive, Spark, PySpark, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96d7c2108f3611f5</t>
+          <t>https://www.indeed.com/viewjob?jk=647d32eb31b1193e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Intern</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Databricks, HDFS, Hive, Spark, PySpark, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, Kafka, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94392d03faa7aff</t>
+          <t>https://www.indeed.com/viewjob?jk=ed859e450f4fb1f8</t>
         </is>
       </c>
     </row>
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0a75acda2378a3</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f7e1ef8e1fdbe0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/ML Engineer Intern</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Databricks, HDFS, Hive, Spark, PySpark, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f5355e15b9a9081</t>
+          <t>https://www.indeed.com/viewjob?jk=96d7c2108f3611f5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/ML Engineer Intern</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tavant Technologies</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Databricks, HDFS, Hive, Spark, PySpark, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad207b0eebcb02ee</t>
+          <t>https://www.indeed.com/viewjob?jk=a94392d03faa7aff</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/ML Engineer Intern</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Databricks, HDFS, Hive, Spark, PySpark, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78e9f6e4739bce7</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0a75acda2378a3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Database Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Verra Mobility</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a766168aef2c43f</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4a511c8a3a07c3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Junior Business Intelligence Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Medpace</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d80e20e6c49d29b</t>
+          <t>https://www.indeed.com/viewjob?jk=83df52bee4296559</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Analyst Engineer - Snowflake Expert</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TKC Holdings</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0839459de9ce2dea</t>
+          <t>https://www.indeed.com/viewjob?jk=0f5355e15b9a9081</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Developer – .NET Full Stack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Tavant Technologies</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7de99645ec71a2</t>
+          <t>https://www.indeed.com/viewjob?jk=ad207b0eebcb02ee</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI-Native Development Platform Engineer Intern, MS - Summer 2027</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb60ceb5f3d080b</t>
+          <t>https://www.indeed.com/viewjob?jk=c78e9f6e4739bce7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, Power BI, Splunk, CI/CD</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe97c58bd1f9ed9b</t>
+          <t>https://www.indeed.com/viewjob?jk=2a766168aef2c43f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Data Analyst Engineer - Snowflake Expert</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>TKC Holdings</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,42 +2131,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, Power BI, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5f97b462b22e62</t>
+          <t>https://www.indeed.com/viewjob?jk=0839459de9ce2dea</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Data Architect (Hadoop/ML/AI/ETL)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ontario, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, HDFS, Hive, YARN, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a4f37408022609</t>
+          <t>https://www.indeed.com/viewjob?jk=c0256d3c6a8c1897</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Azure, Data Factory, Databricks, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a830e46d79d3579</t>
+          <t>https://www.indeed.com/viewjob?jk=36e16b8afdb689b5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>AI-Native Development Platform Engineer Intern, MS - Summer 2027</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f9b93235e29f6c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb60ceb5f3d080b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>API Architect</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SafelyYou</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, ECS, RDS, Spark, Scala, Spark Streaming, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, Power BI, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b87640e62e54b64</t>
+          <t>https://www.indeed.com/viewjob?jk=fe97c58bd1f9ed9b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Architect – Client &amp; Technical Solutions</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, Power BI, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2398bae43cfca4</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5f97b462b22e62</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - AWS Infrastructure &amp; Platform</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ontario, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, AWS CloudFormation</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c080f60278d6dc</t>
+          <t>https://www.indeed.com/viewjob?jk=35a4f37408022609</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer I - Data Platform</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7daae54db1e425f</t>
+          <t>https://www.indeed.com/viewjob?jk=9a830e46d79d3579</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer (Chicago Area)</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bilink Corp</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cc3f410679dfa32</t>
+          <t>https://www.indeed.com/viewjob?jk=1f9b93235e29f6c1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Solution Architect – Solutions and Platform Advisory</t>
+          <t>API Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Trianz</t>
+          <t>SafelyYou</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, RDS, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, API Gateway, ECS, RDS, Spark, Scala, Spark Streaming, Kafka, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=825c83cc17a2a9e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1b87640e62e54b64</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Architect - Healthcare Insights, Revenue Cycle</t>
+          <t>Senior Software Architect – Client &amp; Technical Solutions</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,19 +2491,19 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b58dd53022f160e8</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2398bae43cfca4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Architect - Healthcare Insights, Pharmacy</t>
+          <t>Senior Databricks Data Engineer (Chicago Area)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Bilink Corp</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae3580058d6b9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=2cc3f410679dfa32</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer (SYS ADM 4 TX)</t>
+          <t>Solution Architect – Solutions and Platform Advisory</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>UC Davis</t>
+          <t>Trianz</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, MySQL, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>IAM, RDS, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35d797a405aa8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=825c83cc17a2a9e3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Concentra DevOps Engineer II</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>RJW Logistics</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
+          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87121ab466a00f3</t>
+          <t>https://www.indeed.com/viewjob?jk=7f774f78f05e811f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Power BI, MLOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f774f78f05e811f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1fcc3fc97e62735</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Architect - Healthcare Insights, Revenue Cycle</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Power BI, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fcc3fc97e62735</t>
+          <t>https://www.indeed.com/viewjob?jk=b58dd53022f160e8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Data Architect - Healthcare Insights, Pharmacy</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,49 +2701,49 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbbbfb150a6dcd5b</t>
+          <t>https://www.indeed.com/viewjob?jk=cae3580058d6b9fa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Dev Ops Engineer (SYS ADM 4 TX)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>UC Davis</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Davis, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, MySQL, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ed24d87685f8d1</t>
+          <t>https://www.indeed.com/viewjob?jk=a35d797a405aa8a0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Nodejs, Angularjs, Java)</t>
+          <t>Full-stack Engineer 5, Marketing and Messaging Experimentation</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b68e3f744cf85a2</t>
+          <t>https://www.indeed.com/viewjob?jk=35d91349e906a83d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Engineer Senior | Hybrid</t>
+          <t>Full-stack Engineer 4 (Claude, Node JS, Typescript, Python)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Allianz</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ELT, MLflow, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e49db045a45c992</t>
+          <t>https://www.indeed.com/viewjob?jk=eab3cde603c13024</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer (On-site)</t>
+          <t>Full-stack Engineer 4, Agentic Technology</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa4e2a92b1f4e69</t>
+          <t>https://www.indeed.com/viewjob?jk=7e21b621ca9c3081</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Spark, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e4f1fca016648f</t>
+          <t>https://www.indeed.com/viewjob?jk=dbbbfb150a6dcd5b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4927f7351b05ce</t>
+          <t>https://www.indeed.com/viewjob?jk=34ed24d87685f8d1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Full-Stack Engineer 4 (Nodejs, Angularjs, Java)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58079e817de4277e</t>
+          <t>https://www.indeed.com/viewjob?jk=9b68e3f744cf85a2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>AI Engineer Senior | Hybrid</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Allianz</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ELT, MLflow, CI/CD, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83176228c53939c3</t>
+          <t>https://www.indeed.com/viewjob?jk=8e49db045a45c992</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Cloud Software Engineer (On-site)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c93b5fec88654f</t>
+          <t>https://www.indeed.com/viewjob?jk=faa4e2a92b1f4e69</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, IAM, RDS, Spark, SQL Server, dbt, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151ea1e60e7bac7b</t>
+          <t>https://www.indeed.com/viewjob?jk=99e4f1fca016648f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Engineer II/III (Claims)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Oracle, SQL Server, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b375ce161bec97</t>
+          <t>https://www.indeed.com/viewjob?jk=de4927f7351b05ce</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Java Developer--NAOP (New Account Opening Platform)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93eb43aa251ecf3f</t>
+          <t>https://www.indeed.com/viewjob?jk=58079e817de4277e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Enterprise Data Solution Architect</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Harman</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Novi, MI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Kinesis, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f79d13cbfcddf00</t>
+          <t>https://www.indeed.com/viewjob?jk=83176228c53939c3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e01673a28815832</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c93b5fec88654f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Data Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Harrington Process Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chino, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, Lambda, Step Functions, IAM, RDS, Spark, SQL Server, dbt, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8614d77d4401e0</t>
+          <t>https://www.indeed.com/viewjob?jk=151ea1e60e7bac7b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CJIS Cybersecurity &amp; Google Cloud Architect Specialist</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Harrington Process Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chino, CA, US USA</t>
+          <t>Scottdale, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0cad18cf1700f2</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b1802402649040</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Enterprise Data Solution Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cricut</t>
+          <t>Harman</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Novi, MI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b81ccfe00621caf</t>
+          <t>https://www.indeed.com/viewjob?jk=1f79d13cbfcddf00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Scala, Splunk, MLflow, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fb706820b4a71cf</t>
+          <t>https://www.indeed.com/viewjob?jk=5e01673a28815832</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineers</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Harrington Process Solutions</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Carrollton, TX, US USA</t>
+          <t>Chino, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka, NoSQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cde128110938c0cc</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8614d77d4401e0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer Senior (Python/SQL)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Harrington Process Solutions</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Chino, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD, Airflow, Git</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,67 +3401,67 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe5f4121021f1f1</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0cad18cf1700f2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Graph Engineer (Neo4j, Python, Cloud)</t>
+          <t>Senior Java Developer--NAOP (New Account Opening Platform)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Zions Bancorporation</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4abb4feae415dce7</t>
+          <t>https://www.indeed.com/viewjob?jk=93eb43aa251ecf3f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Graph Engineer (Neo4j, Python, Cloud)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Cricut</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa843bcedcc0999</t>
+          <t>https://www.indeed.com/viewjob?jk=6b81ccfe00621caf</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr AI Platform Engineer- Hybrid in Alpharetta, GA</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1950a9dc92f87ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=202928f0f6bbd46e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer - Football</t>
+          <t>Full-Stack Engineer 5</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tennessee Titans</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, dbt, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7558bccd6171065e</t>
+          <t>https://www.indeed.com/viewjob?jk=efb6e669be8a0fe4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer (Generative AI &amp; Healthcare Data)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Altarum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f49e9b26d98bb56</t>
+          <t>https://www.indeed.com/viewjob?jk=e511f8782fe3c8af</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer- Data Platform</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>UPLIGHT</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, GCP, Spark, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ebb44c59e3216f7</t>
+          <t>https://www.indeed.com/viewjob?jk=6be58b82de098119</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,67 +3646,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990c95bc91fe1ded</t>
+          <t>https://www.indeed.com/viewjob?jk=033490b67917c738</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (US)</t>
+          <t>Full-stack Engineer 4, Agentic Orchestration</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Climavision</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d84804cb26e94786</t>
+          <t>https://www.indeed.com/viewjob?jk=56eaabcd481275c5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Developer Tools &amp; SDKs</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed762a7f7392ce8</t>
+          <t>https://www.indeed.com/viewjob?jk=0fbb69805ce87c47</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr AI/ML Engineer</t>
+          <t>Full-stack Engineer 4, Enterprise Platform - Marketing Technology</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5656fa0a41712d</t>
+          <t>https://www.indeed.com/viewjob?jk=262784cddca9fe3a</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Full-stack Engineer 5, Agentic Orchestration</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab467c318fd6c96</t>
+          <t>https://www.indeed.com/viewjob?jk=027c7b87d09a28a2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Full Stack Engineer - 4 (Java, Python, AWS)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b819455b2c6a14c4</t>
+          <t>https://www.indeed.com/viewjob?jk=429d24776ae7a6f3</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior .NET Application Architect</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ASSYST, Inc.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6237006eb649fb5e</t>
+          <t>https://www.indeed.com/viewjob?jk=912f48418021fdb1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Full-stack Engineer 4 (AWS, Java &amp; Python) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Jenkins, Git, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9a01bf4bcd322b</t>
+          <t>https://www.indeed.com/viewjob?jk=145d72b83ab51ca3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Engineer .NET</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56bf3e137b2717d</t>
+          <t>https://www.indeed.com/viewjob?jk=eb4ecef48f64d451</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Engineer .NET</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd288a3d91533b1</t>
+          <t>https://www.indeed.com/viewjob?jk=6c395ac66d08c231</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Engineer .NET</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d40253975ae472fc</t>
+          <t>https://www.indeed.com/viewjob?jk=8e10d3d79040b3a8</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,42 +4031,812 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8da3c50569b80d</t>
+          <t>https://www.indeed.com/viewjob?jk=191b82ee06f13c9f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Azure Infrastructure &amp; Platform</t>
+          <t>Full-stack Engineer 4 (Cloud Operations Resilience Engineering)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
+          <t>Riverwoods, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38cb7271db1de441</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Data Engineer / Data Analyst</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>NXP Semiconductors</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, RDS, Spark, dbt, Tableau</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43de10da0bbe2c25</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>API Gateway, RDS, Scala, Splunk, MLflow, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fb706820b4a71cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Senior Big Data Engineers</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Carrollton, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka, NoSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cde128110938c0cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Data Engineer Senior (Python/SQL)</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>PNC Financial Services Group</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Lakewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbe5f4121021f1f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Graph Engineer (Neo4j, Python, Cloud)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4abb4feae415dce7</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Graph Engineer (Neo4j, Python, Cloud)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9aa843bcedcc0999</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Sr AI Platform Engineer- Hybrid in Alpharetta, GA</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>OEConnection</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1950a9dc92f87ca2</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Data Engineer - Football</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Tennessee Titans</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, dbt, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7558bccd6171065e</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Data Engineer (Generative AI &amp; Healthcare Data)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Altarum</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, MLflow</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f49e9b26d98bb56</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Software Engineer- Data Platform</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>UPLIGHT</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
           <t>US USA</t>
         </is>
       </c>
-      <c r="D104" t="n">
+      <c r="D114" t="n">
         <v>10.4</v>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, Terraform, Azure Monitor, Python</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d283def45f7dc44</t>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Unity Catalog, GCP, Spark, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ebb44c59e3216f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>OpenShift Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=990c95bc91fe1ded</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer (US)</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Climavision</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d84804cb26e94786</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Enterprise Marketing Management (EMM)</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>I8IS INC.</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d9a49c01a3e9816</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Developer Tools &amp; SDKs</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Keeper Security, Inc.</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ed762a7f7392ce8</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Sr AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da5656fa0a41712d</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ab467c318fd6c96</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Data Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b819455b2c6a14c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Fidelity TalentSource</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Jenkins, Git, SQL</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec9a01bf4bcd322b</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Engineer .NET</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c56bf3e137b2717d</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Engineer .NET</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ddd288a3d91533b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Engineer .NET</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d40253975ae472fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d8da3c50569b80d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-30.xlsx
+++ b/results/job_matches_2026-09-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Enterprise Architect-2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cricut</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,17 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, IAM, RDS, Spark</t>
+          <t>AWS, Lambda, API Gateway, IAM, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0116d4b4ca656c94</t>
+          <t>https://www.indeed.com/viewjob?jk=fffe73772f679b5c</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Apartments.com - Irvine, CA</t>
+          <t>Senior Software Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>ComplexCare Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53ace7c739bbef4</t>
+          <t>https://www.indeed.com/viewjob?jk=057d3f14e1d878f3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer II - Apartments.com - Irvine, CA</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Delta Live Tables, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0ca5cc30971dc02</t>
+          <t>https://www.indeed.com/viewjob?jk=97fa3ea752ece8fd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Business Intelligence Senior Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Sevita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Delta Live Tables, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, SQL Server, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fa3ea752ece8fd</t>
+          <t>https://www.indeed.com/viewjob?jk=28d33086583723d4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Developer &amp; Data Engineer</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WISEcode</t>
+          <t>ThinkPoint Solutions Inc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Medallion Architecture, Spark</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961c34d9312bd45f</t>
+          <t>https://www.indeed.com/viewjob?jk=ca879c0ea096dbfb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>University of Colorado</t>
+          <t>WISEcode</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aurora, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Scala, SQL Server</t>
+          <t>AWS, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551c49c9aa5e5584</t>
+          <t>https://www.indeed.com/viewjob?jk=961c34d9312bd45f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer 5</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>University of Colorado</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Aurora, CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, ECS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a88e47fd9a09b1</t>
+          <t>https://www.indeed.com/viewjob?jk=551c49c9aa5e5584</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer 4 (Python/AWS)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -841,19 +841,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1c8cb0925460a</t>
+          <t>https://www.indeed.com/viewjob?jk=24e9bddd262f10a8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e514f15ff0b1be4b</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a88e47fd9a09b1</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68101adf03f8ea37</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1c8cb0925460a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer 5</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=660e2cf474b4e061</t>
+          <t>https://www.indeed.com/viewjob?jk=e514f15ff0b1be4b</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98b9323fde0e076c</t>
+          <t>https://www.indeed.com/viewjob?jk=68101adf03f8ea37</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zifo</t>
+          <t>HSO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, IAM, RDS, Databricks, Spark</t>
+          <t>API Gateway, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d707249d6f4c2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=e4f187ec5e311d0c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JACK'S</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, IAM, RDS, Google Cloud Platform, Cloud Storage, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5920428f1dd8e6b7</t>
+          <t>https://www.indeed.com/viewjob?jk=99b31bf06061c552</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer - Pre-trade (Gas &amp; Power Industry)</t>
+          <t>Data Architect - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Talan</t>
+          <t>Argano</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, Azure, Data Factory, GCP, BigQuery</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe858dfd726768d</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc9469609f69082</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bollinger Shipyards</t>
+          <t>Precision Analytical Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Raceland, LA, US USA</t>
+          <t>McMinnville, OR, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Oracle, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=664254325a625205</t>
+          <t>https://www.indeed.com/viewjob?jk=dd324299a23feb72</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Precision Analytical Inc</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>McMinnville, OR, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, Scala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd324299a23feb72</t>
+          <t>https://www.indeed.com/viewjob?jk=38f351aee1da6602</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer III: Backend C#</t>
+          <t>Enterprise Data- Data Engineer I</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>GBU Life</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, ECS, RDS, Azure, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b9180a14620aa14</t>
+          <t>https://www.indeed.com/viewjob?jk=647d32eb31b1193e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. AI/ML Engineer - Remote</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38f351aee1da6602</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0d5a4e180f81fe</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. AI Engineer - Asset Management, Investment Data &amp; Reporting</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Cutter Associates</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, dbt, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dbffb9333bd2fe0</t>
+          <t>https://www.indeed.com/viewjob?jk=1aff7f94da1f036f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Enterprise Data- Data Engineer I</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GBU Life</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, Kafka, Snowflake, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=647d32eb31b1193e</t>
+          <t>https://www.indeed.com/viewjob?jk=ed859e450f4fb1f8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Sr. Database Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Verra Mobility</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed859e450f4fb1f8</t>
+          <t>https://www.indeed.com/viewjob?jk=0b4a511c8a3a07c3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Intern</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Databricks, HDFS, Hive, Spark, PySpark, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f7e1ef8e1fdbe0</t>
+          <t>https://www.indeed.com/viewjob?jk=7a5b1e38f7c9f340</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Intern</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Databricks, HDFS, Hive, Spark, PySpark, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96d7c2108f3611f5</t>
+          <t>https://www.indeed.com/viewjob?jk=83df52bee4296559</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Intern</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>FNBO - First National Bank of Omaha</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Databricks, HDFS, Hive, Spark, PySpark, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, RDS, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94392d03faa7aff</t>
+          <t>https://www.indeed.com/viewjob?jk=9f82e2ce098dec35</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Tavant Technologies</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Databricks, HDFS, Hive, Spark, PySpark, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0a75acda2378a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ad207b0eebcb02ee</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Database Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Verra Mobility</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, dbt</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4a511c8a3a07c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c78e9f6e4739bce7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>EMERY SAPP &amp; SONS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, Snowflake, ETL</t>
+          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83df52bee4296559</t>
+          <t>https://www.indeed.com/viewjob?jk=2a766168aef2c43f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Analyst Engineer - Snowflake Expert</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>TKC Holdings</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f5355e15b9a9081</t>
+          <t>https://www.indeed.com/viewjob?jk=0839459de9ce2dea</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect (Hadoop/ML/AI/ETL)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tavant Technologies</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Hadoop, HDFS, Hive, YARN, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad207b0eebcb02ee</t>
+          <t>https://www.indeed.com/viewjob?jk=c0256d3c6a8c1897</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI ML Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78e9f6e4739bce7</t>
+          <t>https://www.indeed.com/viewjob?jk=7821be7fd12fc419</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI-Native Development Platform Engineer Intern, MS - Summer 2027</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a766168aef2c43f</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb60ceb5f3d080b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Analyst Engineer - Snowflake Expert</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TKC Holdings</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, Power BI, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0839459de9ce2dea</t>
+          <t>https://www.indeed.com/viewjob?jk=fe97c58bd1f9ed9b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Architect (Hadoop/ML/AI/ETL)</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, YARN, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, Power BI, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0256d3c6a8c1897</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5f97b462b22e62</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Azure, Data Factory, Databricks, Hadoop, Spark</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e16b8afdb689b5</t>
+          <t>https://www.indeed.com/viewjob?jk=c42d956d4515afe7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI-Native Development Platform Engineer Intern, MS - Summer 2027</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>Elsevier</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,87 +2236,87 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb60ceb5f3d080b</t>
+          <t>https://www.indeed.com/viewjob?jk=14a9b042577646d3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Wilson Elser</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, Power BI, Splunk, CI/CD</t>
+          <t>S3, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe97c58bd1f9ed9b</t>
+          <t>https://www.indeed.com/viewjob?jk=897b2194be6b7543</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, Power BI, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Medallion Architecture, Spark, PySpark, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5f97b462b22e62</t>
+          <t>https://www.indeed.com/viewjob?jk=621931178c25b346</t>
         </is>
       </c>
     </row>
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a830e46d79d3579</t>
+          <t>https://www.indeed.com/viewjob?jk=1f9b93235e29f6c1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Senior Software Architect – Client &amp; Technical Solutions</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f9b93235e29f6c1</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2398bae43cfca4</t>
         </is>
       </c>
     </row>
@@ -2463,52 +2463,52 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Architect – Client &amp; Technical Solutions</t>
+          <t>Software Engineer III Core Platform</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2398bae43cfca4</t>
+          <t>https://www.indeed.com/viewjob?jk=b6d0184975ce5875</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer (Chicago Area)</t>
+          <t>Databricks Architect / Drilling &amp; Energy Domain (Contract &amp; FTE)-4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bilink Corp</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cc3f410679dfa32</t>
+          <t>https://www.indeed.com/viewjob?jk=07d76e817842815f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Solution Architect – Solutions and Platform Advisory</t>
+          <t>Enterprise Cloud Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Trianz</t>
+          <t>Florida Blue (Blue Cross and Blue Shield of Florida)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, RDS, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=825c83cc17a2a9e3</t>
+          <t>https://www.indeed.com/viewjob?jk=af4183097a714f5b</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Architect - Healthcare Insights, Revenue Cycle</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Power BI, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1fcc3fc97e62735</t>
+          <t>https://www.indeed.com/viewjob?jk=b58dd53022f160e8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Architect - Healthcare Insights, Revenue Cycle</t>
+          <t>Data Architect - Healthcare Insights, Pharmacy</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2666,84 +2666,84 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b58dd53022f160e8</t>
+          <t>https://www.indeed.com/viewjob?jk=cae3580058d6b9fa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Architect - Healthcare Insights, Pharmacy</t>
+          <t>Engineer I, Data Engineering</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, Tableau, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae3580058d6b9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=995670ae7da973ef</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer (SYS ADM 4 TX)</t>
+          <t>Full-stack Engineer 5, Marketing and Messaging Experimentation</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>UC Davis</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Davis, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, MySQL, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35d797a405aa8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=35d91349e906a83d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5, Marketing and Messaging Experimentation</t>
+          <t>Full-stack Engineer 4 (Claude, Node JS, Typescript, Python)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,14 +2771,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d91349e906a83d</t>
+          <t>https://www.indeed.com/viewjob?jk=eab3cde603c13024</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Claude, Node JS, Typescript, Python)</t>
+          <t>Full-stack Engineer 4, Agentic Technology</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab3cde603c13024</t>
+          <t>https://www.indeed.com/viewjob?jk=7e21b621ca9c3081</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Agentic Technology</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Spark, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e21b621ca9c3081</t>
+          <t>https://www.indeed.com/viewjob?jk=dbbbfb150a6dcd5b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbbbfb150a6dcd5b</t>
+          <t>https://www.indeed.com/viewjob?jk=34ed24d87685f8d1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer-Wearables &amp; iOT Analytics</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Hill's Pet Nutrition</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Scala, Snowflake, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ed24d87685f8d1</t>
+          <t>https://www.indeed.com/viewjob?jk=15106eef96842e6a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 4 (Nodejs, Angularjs, Java)</t>
+          <t>Cloud Software Engineer (On-site)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b68e3f744cf85a2</t>
+          <t>https://www.indeed.com/viewjob?jk=faa4e2a92b1f4e69</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI Engineer Senior | Hybrid</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Allianz</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ELT, MLflow, CI/CD, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e49db045a45c992</t>
+          <t>https://www.indeed.com/viewjob?jk=99e4f1fca016648f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer (On-site)</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa4e2a92b1f4e69</t>
+          <t>https://www.indeed.com/viewjob?jk=de4927f7351b05ce</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e4f1fca016648f</t>
+          <t>https://www.indeed.com/viewjob?jk=58079e817de4277e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4927f7351b05ce</t>
+          <t>https://www.indeed.com/viewjob?jk=83176228c53939c3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer, Data Platform</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58079e817de4277e</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c93b5fec88654f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>CJIS Cybersecurity &amp; Google Cloud Architect Specialist</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Scottdale, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83176228c53939c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b1802402649040</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Symbotic</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c93b5fec88654f</t>
+          <t>https://www.indeed.com/viewjob?jk=c9b624ac55b1048d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI Data Platform Engineer</t>
+          <t>Analytics Engineer (Power BI)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, IAM, RDS, Spark, SQL Server, dbt, Docker</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=151ea1e60e7bac7b</t>
+          <t>https://www.indeed.com/viewjob?jk=a7bbb3969a8cbc16</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CJIS Cybersecurity &amp; Google Cloud Architect Specialist</t>
+          <t>Enterprise Data Solution Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Harman</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scottdale, GA, US USA</t>
+          <t>Novi, MI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b1802402649040</t>
+          <t>https://www.indeed.com/viewjob?jk=1f79d13cbfcddf00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Enterprise Data Solution Architect</t>
+          <t>Senior Java Developer--NAOP (New Account Opening Platform)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Harman</t>
+          <t>Zions Bancorporation</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Novi, MI, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f79d13cbfcddf00</t>
+          <t>https://www.indeed.com/viewjob?jk=93eb43aa251ecf3f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e01673a28815832</t>
+          <t>https://www.indeed.com/viewjob?jk=c208c5545286f6ca</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Harrington Process Solutions</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chino, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8614d77d4401e0</t>
+          <t>https://www.indeed.com/viewjob?jk=202928f0f6bbd46e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-Stack Engineer 5</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Harrington Process Solutions</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chino, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0cad18cf1700f2</t>
+          <t>https://www.indeed.com/viewjob?jk=efb6e669be8a0fe4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Java Developer--NAOP (New Account Opening Platform)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93eb43aa251ecf3f</t>
+          <t>https://www.indeed.com/viewjob?jk=e511f8782fe3c8af</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cricut</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Spark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b81ccfe00621caf</t>
+          <t>https://www.indeed.com/viewjob?jk=6be58b82de098119</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=202928f0f6bbd46e</t>
+          <t>https://www.indeed.com/viewjob?jk=033490b67917c738</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 5</t>
+          <t>Full-stack Engineer 4, Agentic Orchestration</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,14 +3541,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb6e669be8a0fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=56eaabcd481275c5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e511f8782fe3c8af</t>
+          <t>https://www.indeed.com/viewjob?jk=0fbb69805ce87c47</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 4, Enterprise Platform - Marketing Technology</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be58b82de098119</t>
+          <t>https://www.indeed.com/viewjob?jk=262784cddca9fe3a</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 5, Agentic Orchestration</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,14 +3646,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=033490b67917c738</t>
+          <t>https://www.indeed.com/viewjob?jk=027c7b87d09a28a2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Agentic Orchestration</t>
+          <t>Full Stack Engineer - 4 (Java, Python, AWS)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56eaabcd481275c5</t>
+          <t>https://www.indeed.com/viewjob?jk=429d24776ae7a6f3</t>
         </is>
       </c>
     </row>
@@ -3716,14 +3716,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fbb69805ce87c47</t>
+          <t>https://www.indeed.com/viewjob?jk=912f48418021fdb1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Enterprise Platform - Marketing Technology</t>
+          <t>Full-stack Engineer 4 (AWS, Java &amp; Python) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,14 +3751,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262784cddca9fe3a</t>
+          <t>https://www.indeed.com/viewjob?jk=145d72b83ab51ca3</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5, Agentic Orchestration</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,14 +3786,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=027c7b87d09a28a2</t>
+          <t>https://www.indeed.com/viewjob?jk=eb4ecef48f64d451</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - 4 (Java, Python, AWS)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=429d24776ae7a6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=6c395ac66d08c231</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,14 +3856,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=912f48418021fdb1</t>
+          <t>https://www.indeed.com/viewjob?jk=8e10d3d79040b3a8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (AWS, Java &amp; Python) (Enterprise Platforms Technology)</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=145d72b83ab51ca3</t>
+          <t>https://www.indeed.com/viewjob?jk=191b82ee06f13c9f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Full-stack Engineer 4 (Cloud Operations Resilience Engineering)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,67 +3926,67 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb4ecef48f64d451</t>
+          <t>https://www.indeed.com/viewjob?jk=38cb7271db1de441</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Data Engineer / Data Analyst</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NXP Semiconductors</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, RDS, Spark, dbt, Tableau</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c395ac66d08c231</t>
+          <t>https://www.indeed.com/viewjob?jk=43de10da0bbe2c25</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>API Gateway, RDS, Scala, Splunk, MLflow, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e10d3d79040b3a8</t>
+          <t>https://www.indeed.com/viewjob?jk=6fb706820b4a71cf</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Big Data Engineers</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Carrollton, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191b82ee06f13c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=cde128110938c0cc</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Cloud Operations Resilience Engineering)</t>
+          <t>Data Engineer Senior (Python/SQL)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38cb7271db1de441</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe5f4121021f1f1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer / Data Analyst</t>
+          <t>Graph Engineer (Neo4j, Python, Cloud)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NXP Semiconductors</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, RDS, Spark, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43de10da0bbe2c25</t>
+          <t>https://www.indeed.com/viewjob?jk=4abb4feae415dce7</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Graph Engineer (Neo4j, Python, Cloud)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Scala, Splunk, MLflow, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fb706820b4a71cf</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa843bcedcc0999</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineers</t>
+          <t>Sr AI Platform Engineer- Hybrid in Alpharetta, GA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Carrollton, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka, NoSQL, ETL</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cde128110938c0cc</t>
+          <t>https://www.indeed.com/viewjob?jk=1950a9dc92f87ca2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer Senior (Python/SQL)</t>
+          <t>Data Engineer - Football</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Tennessee Titans</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe5f4121021f1f1</t>
+          <t>https://www.indeed.com/viewjob?jk=7558bccd6171065e</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Graph Engineer (Neo4j, Python, Cloud)</t>
+          <t>Senior Site Reliability Engineer (US)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Climavision</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4abb4feae415dce7</t>
+          <t>https://www.indeed.com/viewjob?jk=d84804cb26e94786</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Graph Engineer (Neo4j, Python, Cloud)</t>
+          <t>Senior Software Engineer, Developer Tools &amp; SDKs</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa843bcedcc0999</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed762a7f7392ce8</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr AI Platform Engineer- Hybrid in Alpharetta, GA</t>
+          <t>Sr AI/ML Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1950a9dc92f87ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=da5656fa0a41712d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer - Football</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Tennessee Titans</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, dbt, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,19 +4346,19 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7558bccd6171065e</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab467c318fd6c96</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer (Generative AI &amp; Healthcare Data)</t>
+          <t>Senior Software Engineer - Enterprise Marketing Management (EMM)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Altarum</t>
+          <t>I8IS INC.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, ELT, dbt, MLflow</t>
+          <t>Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f49e9b26d98bb56</t>
+          <t>https://www.indeed.com/viewjob?jk=6d9a49c01a3e9816</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer- Data Platform</t>
+          <t>Engineering Associate – CIB Operations Technology</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>UPLIGHT</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Unity Catalog, GCP, Spark, Data Modeling, ETL, ELT, MLOps, CI/CD</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ebb44c59e3216f7</t>
+          <t>https://www.indeed.com/viewjob?jk=ce0f5e2c5e2ea8e0</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Engineering Associate – CIB Operations Technology</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Scala, Oracle, PostgreSQL, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990c95bc91fe1ded</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb52199f6ff63f3</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (US)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Climavision</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Jenkins, Git, SQL</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d84804cb26e94786</t>
+          <t>https://www.indeed.com/viewjob?jk=ec9a01bf4bcd322b</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Enterprise Marketing Management (EMM)</t>
+          <t>Senior Engineer .NET</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d9a49c01a3e9816</t>
+          <t>https://www.indeed.com/viewjob?jk=c56bf3e137b2717d</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Developer Tools &amp; SDKs</t>
+          <t>Senior Engineer .NET</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed762a7f7392ce8</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd288a3d91533b1</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sr AI/ML Engineer</t>
+          <t>Senior Engineer .NET</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5656fa0a41712d</t>
+          <t>https://www.indeed.com/viewjob?jk=d40253975ae472fc</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4625,216 +4625,6 @@
         </is>
       </c>
       <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab467c318fd6c96</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Data Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b819455b2c6a14c4</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Fidelity TalentSource</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Durham, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Jenkins, Git, SQL</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9a01bf4bcd322b</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Senior Engineer .NET</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c56bf3e137b2717d</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Senior Engineer .NET</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd288a3d91533b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Senior Engineer .NET</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d40253975ae472fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Truist</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9d8da3c50569b80d</t>
         </is>

--- a/results/job_matches_2026-09-30.xlsx
+++ b/results/job_matches_2026-09-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,12 +573,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Signant Health</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,29 +591,29 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Snowflake, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Cassandra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f8cf55805f4851f</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ae16726479683f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ComplexCare Solutions</t>
+          <t>Signant Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,38 +622,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057d3f14e1d878f3</t>
+          <t>https://www.indeed.com/viewjob?jk=7f8cf55805f4851f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ComplexCare Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Delta Live Tables, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fa3ea752ece8fd</t>
+          <t>https://www.indeed.com/viewjob?jk=057d3f14e1d878f3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Business Intelligence Senior Analyst</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sevita</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, SQL Server, MySQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Delta Live Tables, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28d33086583723d4</t>
+          <t>https://www.indeed.com/viewjob?jk=97fa3ea752ece8fd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ThinkPoint Solutions Inc</t>
+          <t>RelMap Software</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca879c0ea096dbfb</t>
+          <t>https://www.indeed.com/viewjob?jk=d0c20ad72a268b77</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Developer &amp; Data Engineer</t>
+          <t>Senior GCP Data Engineer Consultant – BigQuery &amp; Airflow</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WISEcode</t>
+          <t>Keyhole Software</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Medallion Architecture, Spark</t>
+          <t>AWS, Kinesis, Redshift, S3, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961c34d9312bd45f</t>
+          <t>https://www.indeed.com/viewjob?jk=ce929b1244d5c531</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Senior Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>University of Colorado</t>
+          <t>Sevita</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aurora, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Scala, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, SQL Server, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551c49c9aa5e5584</t>
+          <t>https://www.indeed.com/viewjob?jk=28d33086583723d4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Python/AWS)</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>ThinkPoint Solutions Inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e9bddd262f10a8</t>
+          <t>https://www.indeed.com/viewjob?jk=ca879c0ea096dbfb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer 5</t>
+          <t>Software Developer &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>WISEcode</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SNS, ECS, IAM, RDS, Databricks, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a88e47fd9a09b1</t>
+          <t>https://www.indeed.com/viewjob?jk=961c34d9312bd45f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer 4 (Python/AWS)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -911,19 +911,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1c8cb0925460a</t>
+          <t>https://www.indeed.com/viewjob?jk=24e9bddd262f10a8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Data Engineer 5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e514f15ff0b1be4b</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a88e47fd9a09b1</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68101adf03f8ea37</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1c8cb0925460a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pittsburg, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8788c118957a8b6</t>
+          <t>https://www.indeed.com/viewjob?jk=e514f15ff0b1be4b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pittsburg, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab0ee907185e5f01</t>
+          <t>https://www.indeed.com/viewjob?jk=68101adf03f8ea37</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HSO</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburg, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Dataflow, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4f187ec5e311d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=d8788c118957a8b6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>DevOps Sr Engineer - FinOps</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>DaVita</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Athena, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,102 +1126,102 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99b31bf06061c552</t>
+          <t>https://www.indeed.com/viewjob?jk=48e4c25ad47ec8fe</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Java, Spring, Kafka, CI/CD, AI tools, Glue, RDS, DynamoDB) (Enterprise Platforms Technology )</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>HSO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Dataflow, Scala, Kafka, DynamoDB</t>
+          <t>API Gateway, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Dataflow, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7d57da68f94cf58</t>
+          <t>https://www.indeed.com/viewjob?jk=e4f187ec5e311d0c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud and DevOps</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, Azure, GCP, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b52c9ef8ab310ca</t>
+          <t>https://www.indeed.com/viewjob?jk=8b97a5e70063530e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>arrivia</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d44b35a8a09b64</t>
+          <t>https://www.indeed.com/viewjob?jk=99b31bf06061c552</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-stack Engineer 5 (Java, Spring, Kafka, CI/CD, AI tools, Glue, RDS, DynamoDB) (Enterprise Platforms Technology )</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, Dataflow, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70ab61efb1bae2af</t>
+          <t>https://www.indeed.com/viewjob?jk=d7d57da68f94cf58</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS &amp; Azure) - Contract-to-Hire</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cruz Street</t>
+          <t>arrivia</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vero Beach, FL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, Data Factory</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Dataflow, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=339fc28aca922522</t>
+          <t>https://www.indeed.com/viewjob?jk=53d44b35a8a09b64</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>American Lung Association</t>
+          <t>Southern Hobby Distribution</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a7ef180f361a4b8</t>
+          <t>https://www.indeed.com/viewjob?jk=7d102e066fd479ad</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Southern Hobby Distribution</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb16d38559fc0b69</t>
+          <t>https://www.indeed.com/viewjob?jk=70ab61efb1bae2af</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Backend Software Engineer II – AWS &amp; Data Platforms</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1c49163f9df6e3</t>
+          <t>https://www.indeed.com/viewjob?jk=cab3bff06af76c0e</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Developer / Data Engineer</t>
+          <t>Data Platform Engineer, Cybersecurity Operations</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, Step Functions, S3, RDS, Hadoop, Hive</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=925e167443880f65</t>
+          <t>https://www.indeed.com/viewjob?jk=32ed676bd8243856</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>GCP Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Precision Analytical Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>McMinnville, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,139 +1536,139 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, Scala</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd324299a23feb72</t>
+          <t>https://www.indeed.com/viewjob?jk=dac275bf36488a40</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Applied AI Engineer – Supply Chain</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38f351aee1da6602</t>
+          <t>https://www.indeed.com/viewjob?jk=1e5916ba993e4752</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Enterprise Data- Data Engineer I</t>
+          <t>QA Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GBU Life</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=647d32eb31b1193e</t>
+          <t>https://www.indeed.com/viewjob?jk=ce95a607857d8a63</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer - Remote</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Precision Analytical Inc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>McMinnville, OR, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, Azure, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad0d5a4e180f81fe</t>
+          <t>https://www.indeed.com/viewjob?jk=dd324299a23feb72</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer - Asset Management, Investment Data &amp; Reporting</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cutter Associates</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, Snowflake, dbt, MLflow, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aff7f94da1f036f</t>
+          <t>https://www.indeed.com/viewjob?jk=38f351aee1da6602</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Databricks Engineer - Contract (contract)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, Kafka, Snowflake, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed859e450f4fb1f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e29091a2e4371e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Database Engineer</t>
+          <t>FullStack AWS AI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Verra Mobility</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,112 +1746,112 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Kafka, Snowflake, Oracle, SQL Server, PostgreSQL, dbt</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4a511c8a3a07c3</t>
+          <t>https://www.indeed.com/viewjob?jk=7ce4cac3eae27ecb</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Enterprise Data- Data Engineer I</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>GBU Life</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a5b1e38f7c9f340</t>
+          <t>https://www.indeed.com/viewjob?jk=647d32eb31b1193e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Sr. AI/ML Engineer - Remote</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83df52bee4296559</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0d5a4e180f81fe</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Database Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FNBO - First National Bank of Omaha</t>
+          <t>USA TODAY Co.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, RDS, Scala, Data Modeling</t>
+          <t>AWS, Redshift, SQS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,172 +1861,172 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f82e2ce098dec35</t>
+          <t>https://www.indeed.com/viewjob?jk=81c4013d03e1f5aa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Database Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tavant Technologies</t>
+          <t>LocaliQ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Redshift, SQS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad207b0eebcb02ee</t>
+          <t>https://www.indeed.com/viewjob?jk=4b89b0f12ecf60c4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Database Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>LocaliQ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, SQS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78e9f6e4739bce7</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5463a611effc51</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Database Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EMERY SAPP &amp; SONS</t>
+          <t>USA TODAY Co.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, SQS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a766168aef2c43f</t>
+          <t>https://www.indeed.com/viewjob?jk=3120266f930248e1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Analyst Engineer - Snowflake Expert</t>
+          <t>Senior Database Developer - C13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TKC Holdings</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0839459de9ce2dea</t>
+          <t>https://www.indeed.com/viewjob?jk=75576932f59b7e13</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Architect (Hadoop/ML/AI/ETL)</t>
+          <t>Sr. Database Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>USA TODAY Co.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, HDFS, Hive, YARN, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, SQS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0256d3c6a8c1897</t>
+          <t>https://www.indeed.com/viewjob?jk=9ef70bd0057544fe</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI ML Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, MLOps, MLflow</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7821be7fd12fc419</t>
+          <t>https://www.indeed.com/viewjob?jk=7a5b1e38f7c9f340</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI-Native Development Platform Engineer Intern, MS - Summer 2027</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>Mercury Insurance Company</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Spark, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb60ceb5f3d080b</t>
+          <t>https://www.indeed.com/viewjob?jk=83df52bee4296559</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>FNBO - First National Bank of Omaha</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, Power BI, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, RDS, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe97c58bd1f9ed9b</t>
+          <t>https://www.indeed.com/viewjob?jk=9f82e2ce098dec35</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tavant Technologies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, NoSQL, Power BI, Splunk, CI/CD</t>
+          <t>AWS, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5f97b462b22e62</t>
+          <t>https://www.indeed.com/viewjob?jk=ad207b0eebcb02ee</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42d956d4515afe7</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb1f94893c5712e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Elsevier</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,242 +2246,242 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14a9b042577646d3</t>
+          <t>https://www.indeed.com/viewjob?jk=e0615045d00daaed</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Data Architect (Hadoop/ML/AI/ETL)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>S3, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Hadoop, HDFS, Hive, YARN, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897b2194be6b7543</t>
+          <t>https://www.indeed.com/viewjob?jk=c0256d3c6a8c1897</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>AI-Native Development Platform Engineer Intern, MS - Summer 2027</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Medallion Architecture, Spark, PySpark, ETL</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=621931178c25b346</t>
+          <t>https://www.indeed.com/viewjob?jk=ceb60ceb5f3d080b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Dynatrace Consultant – Professional Services</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ontario, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a4f37408022609</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd30fca3b2ed50b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Data Scientist ADAS Analytics Machine Learning</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, ELT, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f9b93235e29f6c1</t>
+          <t>https://www.indeed.com/viewjob?jk=64507608c433c446</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Architect – Client &amp; Technical Solutions</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, NoSQL, ETL, ELT, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2398bae43cfca4</t>
+          <t>https://www.indeed.com/viewjob?jk=c42d956d4515afe7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>API Architect</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SafelyYou</t>
+          <t>Elsevier</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, ECS, RDS, Spark, Scala, Spark Streaming, Kafka, ETL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b87640e62e54b64</t>
+          <t>https://www.indeed.com/viewjob?jk=14a9b042577646d3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer III Core Platform</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Wilson Elser</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>S3, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6d0184975ce5875</t>
+          <t>https://www.indeed.com/viewjob?jk=897b2194be6b7543</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Databricks Architect / Drilling &amp; Energy Domain (Contract &amp; FTE)-4</t>
+          <t>Data Engineer / Data Platform Engineer Internship Spring 2027 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Kankakee, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d76e817842815f</t>
+          <t>https://www.indeed.com/viewjob?jk=2fea70543399a83d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Enterprise Cloud Architect</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Florida Blue (Blue Cross and Blue Shield of Florida)</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Medallion Architecture, Spark, PySpark, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af4183097a714f5b</t>
+          <t>https://www.indeed.com/viewjob?jk=621931178c25b346</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RJW Logistics</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Ontario, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Databricks, Scala, Oracle, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f774f78f05e811f</t>
+          <t>https://www.indeed.com/viewjob?jk=35a4f37408022609</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Architect - Healthcare Insights, Revenue Cycle</t>
+          <t>API Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>SafelyYou</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, Kinesis, API Gateway, ECS, RDS, Spark, Scala, Spark Streaming, Kafka, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b58dd53022f160e8</t>
+          <t>https://www.indeed.com/viewjob?jk=1b87640e62e54b64</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Architect - Healthcare Insights, Pharmacy</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae3580058d6b9fa</t>
+          <t>https://www.indeed.com/viewjob?jk=9f2965ad3fac6e9b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Engineer I, Data Engineering</t>
+          <t>Data Engineer ADAS Fleet Analytics</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, Tableau, Kubernetes, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,207 +2701,207 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=995670ae7da973ef</t>
+          <t>https://www.indeed.com/viewjob?jk=11ad6f4a442569a8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5, Marketing and Messaging Experimentation</t>
+          <t>Threat &amp; Exposure Management Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d91349e906a83d</t>
+          <t>https://www.indeed.com/viewjob?jk=35d05800edeb9ae7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Claude, Node JS, Typescript, Python)</t>
+          <t>NetSuite, Veeva &amp; AWS Consulting Services — Life Sciences</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>goCloudOffice</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab3cde603c13024</t>
+          <t>https://www.indeed.com/viewjob?jk=713c5c868456cc38</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Agentic Technology</t>
+          <t>Software Engineer III Core Platform</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e21b621ca9c3081</t>
+          <t>https://www.indeed.com/viewjob?jk=b6d0184975ce5875</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer - DevOps</t>
+          <t>Databricks Architect / Drilling &amp; Energy Domain (Contract &amp; FTE)-4</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbbbfb150a6dcd5b</t>
+          <t>https://www.indeed.com/viewjob?jk=07d76e817842815f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise Cloud Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Florida Blue (Blue Cross and Blue Shield of Florida)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ed24d87685f8d1</t>
+          <t>https://www.indeed.com/viewjob?jk=af4183097a714f5b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer-Wearables &amp; iOT Analytics</t>
+          <t>Conversational BI Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hill's Pet Nutrition</t>
+          <t>Sapta Global</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Scala, Snowflake, dbt, Airflow, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Snowflake, ELT, Power BI, MLflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15106eef96842e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=eb3b71809e4f10b7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer (On-site)</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, IAM, RDS, Hive, Spark, Scala, Kafka, dbt, MLflow, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa4e2a92b1f4e69</t>
+          <t>https://www.indeed.com/viewjob?jk=3aaf84515bf65e0a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Engineer I, Data Engineering</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, Tableau, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99e4f1fca016648f</t>
+          <t>https://www.indeed.com/viewjob?jk=995670ae7da973ef</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Full-stack Engineer 5, Marketing and Messaging Experimentation</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4927f7351b05ce</t>
+          <t>https://www.indeed.com/viewjob?jk=35d91349e906a83d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Full-stack Engineer 4 (Claude, Node JS, Typescript, Python)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58079e817de4277e</t>
+          <t>https://www.indeed.com/viewjob?jk=eab3cde603c13024</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Full-stack Engineer 4, Agentic Technology</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83176228c53939c3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e21b621ca9c3081</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Platform</t>
+          <t>Software Engineer - DevOps</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Hadoop, Spark, Scala, Kafka, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Spark, Scala, Kafka, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c93b5fec88654f</t>
+          <t>https://www.indeed.com/viewjob?jk=dbbbfb150a6dcd5b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CJIS Cybersecurity &amp; Google Cloud Architect Specialist</t>
+          <t>BI Developer &amp; Production Support Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sapta Global</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Scottdale, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Dataflow, Snowflake, ELT, Power BI, MLflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b1802402649040</t>
+          <t>https://www.indeed.com/viewjob?jk=f1bbd59742c441b3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Enterprise Semantic Layer &amp; Ontology Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>Sapta Global</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Snowflake, Dimensional Modeling, ELT, Power BI, MLflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9b624ac55b1048d</t>
+          <t>https://www.indeed.com/viewjob?jk=327f8fe14e958d2a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Analytics Engineer (Power BI)</t>
+          <t>Data Engineer-Wearables &amp; iOT Analytics (176270)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Scala, Snowflake, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7bbb3969a8cbc16</t>
+          <t>https://www.indeed.com/viewjob?jk=b5d615a2b140cb52</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Enterprise Data Solution Architect</t>
+          <t>DevOps Forward Deployed Engineer Job Description (AI &amp; Cloud)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Harman</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Novi, MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f79d13cbfcddf00</t>
+          <t>https://www.indeed.com/viewjob?jk=d62003cb9f83aeb6</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Java Developer--NAOP (New Account Opening Platform)</t>
+          <t>DevOps Forward Deployed Engineer Job Description (AI &amp; Cloud)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, Splunk, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93eb43aa251ecf3f</t>
+          <t>https://www.indeed.com/viewjob?jk=e1aa4380989d8a52</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+          <t>DevOps Forward Deployed Engineer Job Description (AI &amp; Cloud)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c208c5545286f6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=2b84f726efca9029</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Site Reliability Engineer- FedRamp</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=202928f0f6bbd46e</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c05522799acac5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 5</t>
+          <t>Senior Site Reliability Infrastructure Engineer- Fedramp</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb6e669be8a0fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=08d06855bbcf79aa</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Site Reliability Engineer (FedRAMP)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Scala, Splunk, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e511f8782fe3c8af</t>
+          <t>https://www.indeed.com/viewjob?jk=964c0e05d4eca96b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Apache Spark Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be58b82de098119</t>
+          <t>https://www.indeed.com/viewjob?jk=e992d6bfc308d8bb</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Data Engineer-Wearables &amp; iOT Analytics</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hill's Pet Nutrition</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Scala, Snowflake, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=033490b67917c738</t>
+          <t>https://www.indeed.com/viewjob?jk=15106eef96842e6a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Agentic Orchestration</t>
+          <t>Cloud Software Engineer (On-site)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, GCP, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56eaabcd481275c5</t>
+          <t>https://www.indeed.com/viewjob?jk=faa4e2a92b1f4e69</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fbb69805ce87c47</t>
+          <t>https://www.indeed.com/viewjob?jk=99e4f1fca016648f</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Enterprise Platform - Marketing Technology</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262784cddca9fe3a</t>
+          <t>https://www.indeed.com/viewjob?jk=de4927f7351b05ce</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5, Agentic Orchestration</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=027c7b87d09a28a2</t>
+          <t>https://www.indeed.com/viewjob?jk=58079e817de4277e</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - 4 (Java, Python, AWS)</t>
+          <t>Senior Application Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>ERCOT/Electric Reliability Council of Texas</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Taylor, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=429d24776ae7a6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f83563c96ec7f7c5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Senior Backend Software Engineer (E-Commerce)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Peloton</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,24 +3706,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, SQS, RDS, GCP, Kafka, PostgreSQL, DynamoDB, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=912f48418021fdb1</t>
+          <t>https://www.indeed.com/viewjob?jk=4f8b45fe2b46e762</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (AWS, Java &amp; Python) (Enterprise Platforms Technology)</t>
+          <t>Full-stack Engineer 5 (Python, AWS, Typescript)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3746,29 +3746,29 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=145d72b83ab51ca3</t>
+          <t>https://www.indeed.com/viewjob?jk=91b49f39edeab7ed</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Symbotic</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,24 +3776,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb4ecef48f64d451</t>
+          <t>https://www.indeed.com/viewjob?jk=c9b624ac55b1048d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3816,29 +3816,29 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c395ac66d08c231</t>
+          <t>https://www.indeed.com/viewjob?jk=c208c5545286f6ca</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Analytics Engineer (Power BI)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e10d3d79040b3a8</t>
+          <t>https://www.indeed.com/viewjob?jk=a7bbb3969a8cbc16</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191b82ee06f13c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=202928f0f6bbd46e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Cloud Operations Resilience Engineering)</t>
+          <t>Full-Stack Engineer 5</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,67 +3926,67 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38cb7271db1de441</t>
+          <t>https://www.indeed.com/viewjob?jk=efb6e669be8a0fe4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer / Data Analyst</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NXP Semiconductors</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, RDS, Spark, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43de10da0bbe2c25</t>
+          <t>https://www.indeed.com/viewjob?jk=e511f8782fe3c8af</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Scala, Splunk, MLflow, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fb706820b4a71cf</t>
+          <t>https://www.indeed.com/viewjob?jk=6be58b82de098119</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineers</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Carrollton, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Kafka, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cde128110938c0cc</t>
+          <t>https://www.indeed.com/viewjob?jk=033490b67917c738</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer Senior (Python/SQL)</t>
+          <t>Full-stack Engineer 4, Agentic Orchestration</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe5f4121021f1f1</t>
+          <t>https://www.indeed.com/viewjob?jk=56eaabcd481275c5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Graph Engineer (Neo4j, Python, Cloud)</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4abb4feae415dce7</t>
+          <t>https://www.indeed.com/viewjob?jk=0fbb69805ce87c47</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Graph Engineer (Neo4j, Python, Cloud)</t>
+          <t>Full-stack Engineer 4, Enterprise Platform - Marketing Technology</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa843bcedcc0999</t>
+          <t>https://www.indeed.com/viewjob?jk=262784cddca9fe3a</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr AI Platform Engineer- Hybrid in Alpharetta, GA</t>
+          <t>Full-stack Engineer 5, Agentic Orchestration</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1950a9dc92f87ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=027c7b87d09a28a2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer - Football</t>
+          <t>Full Stack Engineer - 4 (Java, Python, AWS)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Tennessee Titans</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, dbt, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,67 +4206,67 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7558bccd6171065e</t>
+          <t>https://www.indeed.com/viewjob?jk=429d24776ae7a6f3</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (US)</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Climavision</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d84804cb26e94786</t>
+          <t>https://www.indeed.com/viewjob?jk=912f48418021fdb1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Developer Tools &amp; SDKs</t>
+          <t>Full-stack Engineer 4 (AWS, Java &amp; Python) (Enterprise Platforms Technology)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed762a7f7392ce8</t>
+          <t>https://www.indeed.com/viewjob?jk=145d72b83ab51ca3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr AI/ML Engineer</t>
+          <t>Full Stack Engineer 4</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5656fa0a41712d</t>
+          <t>https://www.indeed.com/viewjob?jk=eb4ecef48f64d451</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab467c318fd6c96</t>
+          <t>https://www.indeed.com/viewjob?jk=6c395ac66d08c231</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Enterprise Marketing Management (EMM)</t>
+          <t>Full-stack Engineer 5</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,94 +4381,94 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d9a49c01a3e9816</t>
+          <t>https://www.indeed.com/viewjob?jk=8e10d3d79040b3a8</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Engineering Associate – CIB Operations Technology</t>
+          <t>Full-stack Engineer 4</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce0f5e2c5e2ea8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=191b82ee06f13c9f</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Engineering Associate – CIB Operations Technology</t>
+          <t>Full-stack Engineer 4 (Cloud Operations Resilience Engineering)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Riverwoods, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, PostgreSQL, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb52199f6ff63f3</t>
+          <t>https://www.indeed.com/viewjob?jk=38cb7271db1de441</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Jenkins, Git, SQL</t>
+          <t>API Gateway, RDS, Scala, Splunk, MLflow, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec9a01bf4bcd322b</t>
+          <t>https://www.indeed.com/viewjob?jk=6fb706820b4a71cf</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Engineer .NET</t>
+          <t>Graph Engineer (Neo4j, Python, Cloud)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56bf3e137b2717d</t>
+          <t>https://www.indeed.com/viewjob?jk=4abb4feae415dce7</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Engineer .NET</t>
+          <t>Graph Engineer (Neo4j, Python, Cloud)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd288a3d91533b1</t>
+          <t>https://www.indeed.com/viewjob?jk=9aa843bcedcc0999</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Engineer .NET</t>
+          <t>Sr AI Platform Engineer- Hybrid in Alpharetta, GA</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d40253975ae472fc</t>
+          <t>https://www.indeed.com/viewjob?jk=1950a9dc92f87ca2</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer - Football</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Tennessee Titans</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, ETL, dbt, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,7 +4626,392 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8da3c50569b80d</t>
+          <t>https://www.indeed.com/viewjob?jk=7558bccd6171065e</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer (US)</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Climavision</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d84804cb26e94786</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>AI and Software Solutions Architect (Remote, Contract)</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>INFUSE</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>MD, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, NoSQL, MLOps, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdfbdeb14e9a28d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>FDM Group</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, Oracle, Python</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c707eed20721e772</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Advisor III, Data &amp; MLOps</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Phillips 66</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Power BI, MLOps, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=399a462361080234</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Fidelity TalentSource</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Jenkins, Git, SQL</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec9a01bf4bcd322b</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer, Marketing</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>IMG Academy</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad035bddd06542e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer, Marketing</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>NCSA College Recruiting</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=730949159ddc5619</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer, Marketing</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>IMG Academy</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c73326af3eb8dfe5</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer, Marketing</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>NCSA College Recruiting</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, Data Modeling, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7df313ae793a47b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Enterprise Marketing Management (EMM)</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>I8IS INC.</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d9a49c01a3e9816</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Developer Tools &amp; SDKs</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Keeper Security, Inc.</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ed762a7f7392ce8</t>
         </is>
       </c>
     </row>
